--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-12-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="254">
   <si>
     <t>SKU</t>
   </si>
@@ -322,57 +322,6 @@
     <t>£41.00</t>
   </si>
   <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/25mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/30mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/40mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/50mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/60mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/70mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/75mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/80mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/90mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/100mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/110mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/120mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/130mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/140mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/150mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/50mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm-10-8m2-pack</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/100mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm-5-4m2-pack</t>
-  </si>
-  <si>
     <t>£11.09</t>
   </si>
   <si>
@@ -778,7 +727,7 @@
     <t>£95.22</t>
   </si>
   <si>
-    <t>£128.88</t>
+    <t>£515.52</t>
   </si>
   <si>
     <t>£10.34</t>
@@ -1266,7 +1215,7 @@
         <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
         <v>67</v>
@@ -1275,34 +1224,34 @@
         <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="L2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="N2" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="O2" t="s">
         <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="Q2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R2" t="s">
+        <v>222</v>
+      </c>
+      <c r="S2" t="s">
         <v>238</v>
-      </c>
-      <c r="R2" t="s">
-        <v>239</v>
-      </c>
-      <c r="S2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1325,43 +1274,43 @@
         <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="I3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="L3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="M3" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="N3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="O3" t="s">
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="Q3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R3" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="S3" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1384,43 +1333,43 @@
         <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I4" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="J4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="L4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="N4" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="O4" t="s">
         <v>91</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R4" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="S4" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1443,43 +1392,43 @@
         <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="J5" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="L5" t="s">
         <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="N5" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="O5" t="s">
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="Q5" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R5" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="S5" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1502,43 +1451,43 @@
         <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
         <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="K6" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L6" t="s">
         <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="N6" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="O6" t="s">
         <v>91</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="Q6" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R6" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="S6" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1561,43 +1510,43 @@
         <v>96</v>
       </c>
       <c r="G7" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s">
         <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="L7" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="M7" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="N7" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="O7" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="Q7" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R7" t="s">
         <v>90</v>
       </c>
       <c r="S7" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1620,43 +1569,43 @@
         <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="K8" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L8" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="N8" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="O8" t="s">
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="Q8" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R8" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="S8" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1679,43 +1628,43 @@
         <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I9" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="J9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="L9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="M9" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="N9" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="O9" t="s">
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q9" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R9" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="S9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1738,28 +1687,28 @@
         <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="K10" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="L10" t="s">
         <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="N10" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="O10" t="s">
         <v>91</v>
@@ -1768,13 +1717,13 @@
         <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R10" t="s">
         <v>90</v>
       </c>
       <c r="S10" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1797,43 +1746,43 @@
         <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="K11" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="M11" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="N11" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="O11" t="s">
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R11" t="s">
+        <v>229</v>
+      </c>
+      <c r="S11" t="s">
         <v>246</v>
-      </c>
-      <c r="S11" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1856,7 +1805,7 @@
         <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
         <v>77</v>
@@ -1865,16 +1814,16 @@
         <v>77</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="K12" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s">
         <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="N12" t="s">
         <v>91</v>
@@ -1883,7 +1832,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="Q12" t="s">
         <v>91</v>
@@ -1915,43 +1864,43 @@
         <v>99</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s">
+        <v>164</v>
+      </c>
+      <c r="M13" t="s">
         <v>181</v>
       </c>
-      <c r="M13" t="s">
-        <v>198</v>
-      </c>
       <c r="N13" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="O13" t="s">
         <v>91</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="Q13" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R13" t="s">
+        <v>230</v>
+      </c>
+      <c r="S13" t="s">
         <v>247</v>
-      </c>
-      <c r="S13" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1974,40 +1923,40 @@
         <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="J14" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="K14" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="M14" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="N14" t="s">
+        <v>200</v>
+      </c>
+      <c r="O14" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" t="s">
         <v>217</v>
       </c>
-      <c r="O14" t="s">
-        <v>91</v>
-      </c>
-      <c r="P14" t="s">
-        <v>234</v>
-      </c>
       <c r="Q14" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R14" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="S14" t="s">
         <v>91</v>
@@ -2033,40 +1982,40 @@
         <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="J15" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O15" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" t="s">
         <v>218</v>
       </c>
-      <c r="O15" t="s">
-        <v>91</v>
-      </c>
-      <c r="P15" t="s">
-        <v>235</v>
-      </c>
       <c r="Q15" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R15" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="S15" t="s">
         <v>91</v>
@@ -2092,43 +2041,43 @@
         <v>101</v>
       </c>
       <c r="G16" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s">
         <v>81</v>
       </c>
       <c r="I16" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="J16" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="L16" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="M16" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s">
+        <v>202</v>
+      </c>
+      <c r="O16" t="s">
+        <v>91</v>
+      </c>
+      <c r="P16" t="s">
         <v>219</v>
       </c>
-      <c r="O16" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" t="s">
-        <v>236</v>
-      </c>
       <c r="Q16" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="R16" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="S16" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2210,10 +2159,10 @@
         <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
         <v>91</v>
@@ -2222,13 +2171,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="L18" t="s">
         <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s">
         <v>91</v>
@@ -2243,10 +2192,10 @@
         <v>91</v>
       </c>
       <c r="R18" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="S18" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2269,10 +2218,10 @@
         <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I19" t="s">
         <v>91</v>
@@ -2281,13 +2230,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="L19" t="s">
         <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s">
         <v>91</v>
@@ -2302,10 +2251,10 @@
         <v>91</v>
       </c>
       <c r="R19" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="S19" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2346,7 +2295,7 @@
         <v>91</v>
       </c>
       <c r="M20" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="N20" t="s">
         <v>91</v>
@@ -2405,7 +2354,7 @@
         <v>91</v>
       </c>
       <c r="M21" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N21" t="s">
         <v>91</v>
@@ -2464,7 +2413,7 @@
         <v>91</v>
       </c>
       <c r="M22" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s">
         <v>91</v>
@@ -2508,7 +2457,7 @@
         <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
         <v>91</v>
@@ -2517,31 +2466,31 @@
         <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="L23" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="M23" t="s">
         <v>91</v>
       </c>
       <c r="N23" t="s">
+        <v>203</v>
+      </c>
+      <c r="O23" t="s">
+        <v>91</v>
+      </c>
+      <c r="P23" t="s">
         <v>220</v>
       </c>
-      <c r="O23" t="s">
-        <v>91</v>
-      </c>
-      <c r="P23" t="s">
-        <v>237</v>
-      </c>
       <c r="Q23" t="s">
         <v>91</v>
       </c>
       <c r="R23" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="S23" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2567,7 +2516,7 @@
         <v>91</v>
       </c>
       <c r="H24" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I24" t="s">
         <v>91</v>
@@ -2576,16 +2525,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s">
         <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s">
         <v>91</v>
@@ -2597,10 +2546,10 @@
         <v>91</v>
       </c>
       <c r="R24" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="S24" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2626,7 +2575,7 @@
         <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I25" t="s">
         <v>91</v>
@@ -2635,16 +2584,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="M25" t="s">
         <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="O25" t="s">
         <v>91</v>
@@ -2656,10 +2605,10 @@
         <v>91</v>
       </c>
       <c r="R25" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="S25" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
